--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0</v>
+        <v>0.8783783783783784</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.8783783783783784</v>
+        <v>0.9</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="C2">
-        <v>0.6785714285714286</v>
+        <v>0.6808510638297872</v>
       </c>
       <c r="D2">
-        <v>0.4090909090909091</v>
+        <v>0.3781512605042017</v>
       </c>
       <c r="E2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
